--- a/aux_info/hakan_proteins/DG_amino_acids.xlsx
+++ b/aux_info/hakan_proteins/DG_amino_acids.xlsx
@@ -5,10 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Ref A" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Ref B" sheetId="2" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -44,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="44">
   <si>
     <t xml:space="preserve">Residue</t>
   </si>
@@ -170,6 +171,12 @@
   </si>
   <si>
     <t xml:space="preserve">B) https://doi.org/10.1021/bi00104a017 (    Kim A. SharpAnthony NichollsRichard FriedmanBarry Honig)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C) http://www.pnas.org/cgi/doi/10.1073/pnas.1507565112 (Wolfenden)</t>
   </si>
 </sst>
 </file>
@@ -285,7 +292,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -340,6 +347,14 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -428,13 +443,13 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.82"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="2" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="25.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="25.58"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.89"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="15.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="20.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="21.04"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12.51"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="20.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="21.04"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -463,7 +478,7 @@
       <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="K1" s="0" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="M1" s="3" t="s">
@@ -485,11 +500,11 @@
         <v>2243.76543337495</v>
       </c>
       <c r="D2" s="5" t="n">
-        <v>179.6</v>
+        <v>181.233333333333</v>
       </c>
       <c r="E2" s="5" t="n">
         <f aca="false">D2/C2</f>
-        <v>0.0800440176716045</v>
+        <v>0.0807719606682468</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>9</v>
@@ -508,21 +523,21 @@
         <f aca="false">H2-$H$13</f>
         <v>1.42</v>
       </c>
-      <c r="K2" s="0" t="n">
+      <c r="K2" s="1" t="n">
         <f aca="false">I2*$G$32</f>
         <v>3608.76</v>
       </c>
-      <c r="L2" s="0" t="n">
+      <c r="L2" s="1" t="n">
         <f aca="false">J2*$G$32</f>
         <v>5890.16</v>
       </c>
-      <c r="M2" s="0" t="n">
+      <c r="M2" s="1" t="n">
         <f aca="false">$D$2/K2</f>
-        <v>0.0497677872731908</v>
-      </c>
-      <c r="N2" s="0" t="n">
+        <v>0.0502203896444578</v>
+      </c>
+      <c r="N2" s="1" t="n">
         <f aca="false">$D$2/L2</f>
-        <v>0.0304915316392084</v>
+        <v>0.0307688302751255</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -537,11 +552,11 @@
         <v>-673.129630012486</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>321.833333333333</v>
+        <v>276.3</v>
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">D3/C3</f>
-        <v>-0.478114940991921</v>
+        <v>-0.410470714229108</v>
       </c>
       <c r="F3" s="6"/>
       <c r="G3" s="2"/>
@@ -559,11 +574,11 @@
         <v>-5048.47222509364</v>
       </c>
       <c r="D4" s="8" t="n">
-        <v>321.833333333333</v>
+        <v>276.3</v>
       </c>
       <c r="E4" s="5" t="n">
-        <f aca="false">D4/C4</f>
-        <v>-0.0637486587989228</v>
+        <f aca="false">D5/C4</f>
+        <v>-0.0209040138536913</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="2"/>
@@ -580,12 +595,12 @@
         <f aca="false">LN(10)*$B$33*$B$32*B5</f>
         <v>-897.506173349981</v>
       </c>
-      <c r="D5" s="5" t="n">
-        <v>131.666666666667</v>
+      <c r="D5" s="8" t="n">
+        <v>105.533333333333</v>
       </c>
       <c r="E5" s="5" t="n">
-        <f aca="false">D5/C5</f>
-        <v>-0.146702797792705</v>
+        <f aca="false">D7/C5</f>
+        <v>-0.116285179718724</v>
       </c>
       <c r="F5" s="6"/>
       <c r="G5" s="2"/>
@@ -602,12 +617,12 @@
         <f aca="false">LN(10)*$B$33*$B$32*B6</f>
         <v>-392.658950840617</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>130.3</v>
+      <c r="D6" s="8" t="n">
+        <v>105.533333333333</v>
       </c>
       <c r="E6" s="5" t="n">
-        <f aca="false">D6/C6</f>
-        <v>-0.331840136895007</v>
+        <f aca="false">D8/C6</f>
+        <v>-0.644240163442366</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="2"/>
@@ -625,11 +640,11 @@
         <v>-5889.88426260925</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>130.3</v>
+        <v>104.366666666667</v>
       </c>
       <c r="E7" s="5" t="n">
-        <f aca="false">D7/C7</f>
-        <v>-0.0221226757930005</v>
+        <f aca="false">D10/C7</f>
+        <v>-0.0332038216621984</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="2"/>
@@ -647,11 +662,11 @@
         <v>4599.71913841865</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>273.433333333333</v>
+        <v>252.966666666667</v>
       </c>
       <c r="E8" s="5" t="n">
-        <f aca="false">D8/C8</f>
-        <v>0.0594456585510865</v>
+        <f aca="false">D11/C8</f>
+        <v>0.0423504118703584</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="2"/>
@@ -669,11 +684,11 @@
         <v>-2187.67129754058</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>273.433333333333</v>
+        <v>252.966666666667</v>
       </c>
       <c r="E9" s="5" t="n">
-        <f aca="false">D9/C9</f>
-        <v>-0.124988307722797</v>
+        <f aca="false">D13/C9</f>
+        <v>-0.0422214556503562</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="2"/>
@@ -691,11 +706,11 @@
         <v>560.941358343738</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>216.033333333333</v>
+        <v>195.566666666667</v>
       </c>
       <c r="E10" s="5" t="n">
-        <f aca="false">D10/C10</f>
-        <v>0.385126413162337</v>
+        <f aca="false">D14/C10</f>
+        <v>0.361059726334572</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="2"/>
@@ -713,11 +728,11 @@
         <v>2019.38889003746</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>215.3</v>
+        <v>194.8</v>
       </c>
       <c r="E11" s="5" t="n">
-        <f aca="false">D11/C11</f>
-        <v>0.106616413045635</v>
+        <f aca="false">D16/C11</f>
+        <v>0.20654763530578</v>
       </c>
       <c r="F11" s="6"/>
       <c r="G11" s="2"/>
@@ -735,11 +750,11 @@
         <v>-5497.22531176863</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>215.3</v>
+        <v>194.8</v>
       </c>
       <c r="E12" s="5" t="n">
-        <f aca="false">D12/C12</f>
-        <v>-0.0391652129555394</v>
+        <f aca="false">D17/C12</f>
+        <v>-0.0721879331530727</v>
       </c>
       <c r="F12" s="6"/>
       <c r="G12" s="2"/>
@@ -757,7 +772,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>95.7666666666667</v>
+        <v>92.3666666666667</v>
       </c>
       <c r="E13" s="5"/>
       <c r="F13" s="6"/>
@@ -775,11 +790,11 @@
         <f aca="false">H13-$H$13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <f aca="false">I13*$G$32</f>
         <v>0</v>
       </c>
-      <c r="L13" s="0" t="n">
+      <c r="L13" s="1" t="n">
         <f aca="false">J13*$G$32</f>
         <v>0</v>
       </c>
@@ -799,8 +814,8 @@
         <v>202.533333333333</v>
       </c>
       <c r="E14" s="5" t="n">
-        <f aca="false">D14/C14</f>
-        <v>0.0925794170088646</v>
+        <f aca="false">D20/C14</f>
+        <v>0.0883435582319614</v>
       </c>
       <c r="F14" s="6"/>
       <c r="G14" s="2"/>
@@ -821,8 +836,8 @@
         <v>202.533333333333</v>
       </c>
       <c r="E15" s="5" t="n">
-        <f aca="false">D15/C15</f>
-        <v>-0.0429833007541157</v>
+        <f aca="false">D21/C15</f>
+        <v>-0.0844739292799368</v>
       </c>
       <c r="F15" s="6"/>
       <c r="G15" s="2"/>
@@ -840,11 +855,11 @@
         <v>8694.59105432794</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>420.466666666667</v>
+        <v>417.1</v>
       </c>
       <c r="E16" s="9" t="n">
-        <f aca="false">D16/C16</f>
-        <v>0.0483595679244016</v>
+        <f aca="false">D22/C16</f>
+        <v>0.0226079254836052</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>9</v>
@@ -863,21 +878,21 @@
         <f aca="false">H16-$H$13</f>
         <v>6.23</v>
       </c>
-      <c r="K16" s="0" t="n">
+      <c r="K16" s="1" t="n">
         <f aca="false">I16*$G$32</f>
         <v>16509.04</v>
       </c>
-      <c r="L16" s="0" t="n">
+      <c r="L16" s="1" t="n">
         <f aca="false">J16*$G$32</f>
         <v>25842.04</v>
       </c>
-      <c r="M16" s="0" t="n">
+      <c r="M16" s="1" t="n">
         <f aca="false">$D$2/K16</f>
-        <v>0.0108788881727829</v>
-      </c>
-      <c r="N16" s="0" t="n">
+        <v>0.0109778238670046</v>
+      </c>
+      <c r="N16" s="1" t="n">
         <f aca="false">$D$2/L16</f>
-        <v>0.00694991571872809</v>
+        <v>0.00701312022322283</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -892,11 +907,11 @@
         <v>9199.4382768373</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>401.2</v>
+        <v>396.833333333333</v>
       </c>
       <c r="E17" s="9" t="n">
-        <f aca="false">D17/C17</f>
-        <v>0.04361135842502</v>
+        <f aca="false">D23/C17</f>
+        <v>0.0104354197627167</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>9</v>
@@ -915,21 +930,21 @@
         <f aca="false">H17-$H$13</f>
         <v>6.38</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <f aca="false">I17*$G$32</f>
         <v>16509.04</v>
       </c>
-      <c r="L17" s="0" t="n">
+      <c r="L17" s="1" t="n">
         <f aca="false">J17*$G$32</f>
         <v>26464.24</v>
       </c>
-      <c r="M17" s="0" t="n">
+      <c r="M17" s="1" t="n">
         <f aca="false">$D$2/K17</f>
-        <v>0.0108788881727829</v>
-      </c>
-      <c r="N17" s="0" t="n">
+        <v>0.0109778238670046</v>
+      </c>
+      <c r="N17" s="1" t="n">
         <f aca="false">$D$2/L17</f>
-        <v>0.0067865164463442</v>
+        <v>0.00684823495151697</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -944,11 +959,11 @@
         <v>-673.129630012486</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>287.433333333333</v>
+        <v>258.966666666667</v>
       </c>
       <c r="E18" s="5" t="n">
-        <f aca="false">D18/C18</f>
-        <v>-0.427010371431728</v>
+        <f aca="false">D24/C18</f>
+        <v>-0.300387905961367</v>
       </c>
       <c r="F18" s="6"/>
       <c r="G18" s="2"/>
@@ -966,11 +981,11 @@
         <v>-6394.73148511861</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>287.433333333333</v>
+        <v>258.966666666667</v>
       </c>
       <c r="E19" s="5" t="n">
-        <f aca="false">D19/C19</f>
-        <v>-0.0449484601507082</v>
+        <f aca="false">D25/C19</f>
+        <v>-0.0740505421432171</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="2"/>
@@ -988,11 +1003,11 @@
         <v>7965.36728848108</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>186.366666666667</v>
+        <v>193.266666666667</v>
       </c>
       <c r="E20" s="10" t="n">
-        <f aca="false">D20/C20</f>
-        <v>0.0233971215534752</v>
+        <f aca="false">D26/C20</f>
+        <v>0.0398642425180476</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>9</v>
@@ -1011,21 +1026,21 @@
         <f aca="false">H20-$H$13</f>
         <v>3.39</v>
       </c>
-      <c r="K20" s="0" t="n">
+      <c r="K20" s="1" t="n">
         <f aca="false">I20*$G$32</f>
         <v>5848.68</v>
       </c>
-      <c r="L20" s="0" t="n">
+      <c r="L20" s="1" t="n">
         <f aca="false">J20*$G$32</f>
         <v>14061.72</v>
       </c>
-      <c r="M20" s="0" t="n">
+      <c r="M20" s="1" t="n">
         <f aca="false">$D$2/K20</f>
-        <v>0.0307077836366496</v>
-      </c>
-      <c r="N20" s="0" t="n">
+        <v>0.030987048929559</v>
+      </c>
+      <c r="N20" s="1" t="n">
         <f aca="false">$D$2/L20</f>
-        <v>0.0127722639904649</v>
+        <v>0.012888418581321</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1040,11 +1055,11 @@
         <v>9143.34414100293</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>394.3</v>
+        <v>398.033333333333</v>
       </c>
       <c r="E21" s="9" t="n">
-        <f aca="false">D21/C21</f>
-        <v>0.043124265467793</v>
+        <f aca="false">D27/C21</f>
+        <v>0.0360918275535676</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>9</v>
@@ -1063,21 +1078,21 @@
         <f aca="false">H21-$H$13</f>
         <v>4.46</v>
       </c>
-      <c r="K21" s="0" t="n">
+      <c r="K21" s="1" t="n">
         <f aca="false">I21*$G$32</f>
         <v>8461.92</v>
       </c>
-      <c r="L21" s="0" t="n">
+      <c r="L21" s="1" t="n">
         <f aca="false">J21*$G$32</f>
         <v>18500.08</v>
       </c>
-      <c r="M21" s="0" t="n">
+      <c r="M21" s="1" t="n">
         <f aca="false">$D$2/K21</f>
-        <v>0.0212244975135667</v>
-      </c>
-      <c r="N21" s="0" t="n">
+        <v>0.0214175191130776</v>
+      </c>
+      <c r="N21" s="1" t="n">
         <f aca="false">$D$2/L21</f>
-        <v>0.00970806612728161</v>
+        <v>0.00979635403378436</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1092,11 +1107,11 @@
         <v>4319.24845924678</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>181.333333333333</v>
+        <v>196.566666666667</v>
       </c>
       <c r="E22" s="9" t="n">
-        <f aca="false">D22/C22</f>
-        <v>0.0419826122632813</v>
+        <f aca="false">D27/C22</f>
+        <v>0.076402180405604</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>9</v>
@@ -1115,11 +1130,11 @@
         <v>-448.75308667499</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>109.966666666667</v>
+        <v>96</v>
       </c>
       <c r="E23" s="5" t="n">
-        <f aca="false">D23/C23</f>
-        <v>-0.24504938223703</v>
+        <f aca="false">D27/C23</f>
+        <v>-0.735370986403939</v>
       </c>
       <c r="F23" s="6"/>
       <c r="G23" s="2"/>
@@ -1136,11 +1151,11 @@
         <v>1851.10648253434</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>208.333333333333</v>
+        <v>202.2</v>
       </c>
       <c r="E24" s="5" t="n">
-        <f aca="false">D24/C24</f>
-        <v>0.112545299419029</v>
+        <f aca="false">D27/C24</f>
+        <v>0.178271754279743</v>
       </c>
       <c r="F24" s="6"/>
       <c r="G24" s="2"/>
@@ -1157,11 +1172,11 @@
         <v>6394.73148511861</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>469.8</v>
+        <v>473.533333333333</v>
       </c>
       <c r="E25" s="10" t="n">
-        <f aca="false">D25/C25</f>
-        <v>0.0734667282110729</v>
+        <f aca="false">D27/C25</f>
+        <v>0.0516049815020308</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>9</v>
@@ -1180,21 +1195,21 @@
         <f aca="false">H25-$H$13</f>
         <v>4.26</v>
       </c>
-      <c r="K25" s="0" t="n">
+      <c r="K25" s="1" t="n">
         <f aca="false">I25*$G$32</f>
         <v>5765.72</v>
       </c>
-      <c r="L25" s="0" t="n">
+      <c r="L25" s="1" t="n">
         <f aca="false">J25*$G$32</f>
         <v>17670.48</v>
       </c>
-      <c r="M25" s="0" t="n">
+      <c r="M25" s="1" t="n">
         <f aca="false">$D$2/K25</f>
-        <v>0.0311496222501266</v>
-      </c>
-      <c r="N25" s="0" t="n">
+        <v>0.0314329057486894</v>
+      </c>
+      <c r="N25" s="1" t="n">
         <f aca="false">$D$2/L25</f>
-        <v>0.0101638438797361</v>
+        <v>0.0102562767583752</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1209,11 +1224,11 @@
         <v>4936.2839534249</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>320.866666666667</v>
+        <v>317.533333333333</v>
       </c>
       <c r="E26" s="5" t="n">
-        <f aca="false">D26/C26</f>
-        <v>0.0650016631324548</v>
+        <f aca="false">D27/C26</f>
+        <v>0.0668519078549035</v>
       </c>
       <c r="F26" s="6"/>
       <c r="G26" s="2"/>
@@ -1230,11 +1245,11 @@
         <v>6619.10802845611</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>328.733333333333</v>
+        <v>330</v>
       </c>
       <c r="E27" s="9" t="n">
         <f aca="false">D27/C27</f>
-        <v>0.0496642949352209</v>
+        <v>0.0498556600951823</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>9</v>
@@ -1253,21 +1268,21 @@
         <f aca="false">H27-$H$13</f>
         <v>4.82</v>
       </c>
-      <c r="K27" s="0" t="n">
+      <c r="K27" s="1" t="n">
         <f aca="false">I27*$G$32</f>
         <v>12858.8</v>
       </c>
-      <c r="L27" s="0" t="n">
+      <c r="L27" s="1" t="n">
         <f aca="false">J27*$G$32</f>
         <v>19993.36</v>
       </c>
-      <c r="M27" s="0" t="n">
+      <c r="M27" s="1" t="n">
         <f aca="false">$D$2/K27</f>
-        <v>0.0139670886863471</v>
-      </c>
-      <c r="N27" s="0" t="n">
+        <v>0.0140941093518317</v>
+      </c>
+      <c r="N27" s="1" t="n">
         <f aca="false">$D$2/L27</f>
-        <v>0.00898298235014025</v>
+        <v>0.00906467613914486</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1276,31 +1291,28 @@
       <c r="J28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
       <c r="E29" s="11" t="n">
         <f aca="false">AVERAGE(E2,E16,E17,E20,E21,E22,E25,E27)</f>
-        <v>0.0504562458064837</v>
+        <v>0.0459542747486251</v>
       </c>
       <c r="F29" s="6" t="n">
         <f aca="false">E29/2</f>
-        <v>0.0252281229032418</v>
+        <v>0.0229771373743126</v>
       </c>
       <c r="G29" s="5"/>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0"/>
       <c r="E30" s="12" t="n">
         <f aca="false">STDEV(E2,E16,E17,E20,E21,E22,E25,E27)</f>
-        <v>0.0181837874354137</v>
+        <v>0.024282547956706</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0"/>
       <c r="E31" s="12"/>
-      <c r="G31" s="0" t="s">
+      <c r="G31" s="1" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1314,16 +1326,16 @@
       <c r="C32" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G32" s="0" t="n">
+      <c r="G32" s="1" t="n">
         <v>4148</v>
       </c>
-      <c r="M32" s="0" t="n">
+      <c r="M32" s="1" t="n">
         <f aca="false">AVERAGE(M2:M27)</f>
-        <v>0.0240820793864924</v>
-      </c>
-      <c r="N32" s="0" t="n">
+        <v>0.0243010886459464</v>
+      </c>
+      <c r="N32" s="1" t="n">
         <f aca="false">AVERAGE(N2:N27)</f>
-        <v>0.0122650171645577</v>
+        <v>0.0123765587089272</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1359,4 +1371,489 @@
   </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F1048576"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20.07"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="14" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="15" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B2</f>
+        <v>12043.8991549246</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>181.233333333333</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <f aca="false">D2/C2</f>
+        <v>0.0150477292280572</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="15" t="n">
+        <v>4.32</v>
+      </c>
+      <c r="C3" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B3</f>
+        <v>24658.5992176656</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>276.3</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>-0.410470714229108</v>
+      </c>
+      <c r="F3" s="15"/>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="15" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B4</f>
+        <v>27855.084301437</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>105.533333333333</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>-0.116285179718724</v>
+      </c>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="15" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B5</f>
+        <v>18779.3498671573</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>104.366666666667</v>
+      </c>
+      <c r="E5" s="0" t="n">
+        <v>-0.0332038216621984</v>
+      </c>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="15" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B6</f>
+        <v>4680.56744409393</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>252.966666666667</v>
+      </c>
+      <c r="E6" s="0" t="n">
+        <v>0.0423504118703584</v>
+      </c>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="15" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B7</f>
+        <v>570.800907816333</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>195.566666666667</v>
+      </c>
+      <c r="E7" s="0" t="n">
+        <v>0.361059726334572</v>
+      </c>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="15" t="n">
+        <v>-0.98</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B8</f>
+        <v>-5593.84889660006</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>194.8</v>
+      </c>
+      <c r="E8" s="0" t="n">
+        <v>-0.0721879331530727</v>
+      </c>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B9</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>92.3666666666667</v>
+      </c>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="15" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B10</f>
+        <v>2226.1235404837</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>202.533333333333</v>
+      </c>
+      <c r="E10" s="0" t="n">
+        <v>0.0883435582319614</v>
+      </c>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B11</f>
+        <v>8847.41407115316</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>417.1</v>
+      </c>
+      <c r="E11" s="0" t="n">
+        <v>0.0226079254836052</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B12</f>
+        <v>9361.13488818786</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>396.833333333333</v>
+      </c>
+      <c r="E12" s="0" t="n">
+        <v>0.0104354197627167</v>
+      </c>
+      <c r="F12" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B13</f>
+        <v>-684.961089379599</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>258.966666666667</v>
+      </c>
+      <c r="E13" s="0" t="n">
+        <v>-0.300387905961367</v>
+      </c>
+      <c r="F13" s="15"/>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B14</f>
+        <v>8105.37289099192</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>193.266666666667</v>
+      </c>
+      <c r="E14" s="0" t="n">
+        <v>0.0398642425180476</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B15</f>
+        <v>9304.05479740622</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>398.033333333333</v>
+      </c>
+      <c r="E15" s="0" t="n">
+        <v>0.0360918275535676</v>
+      </c>
+      <c r="F15" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B16</f>
+        <v>4395.16699018576</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>196.566666666667</v>
+      </c>
+      <c r="E16" s="0" t="n">
+        <v>0.076402180405604</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B17</f>
+        <v>-456.640726253066</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="E17" s="0" t="n">
+        <v>-0.735370986403939</v>
+      </c>
+      <c r="F17" s="15"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B18</f>
+        <v>1883.6429957939</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>202.2</v>
+      </c>
+      <c r="E18" s="0" t="n">
+        <v>0.178271754279743</v>
+      </c>
+      <c r="F18" s="15"/>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="15" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B19</f>
+        <v>6507.13034910619</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>473.533333333333</v>
+      </c>
+      <c r="E19" s="0" t="n">
+        <v>0.0516049815020308</v>
+      </c>
+      <c r="F19" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="15" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B20</f>
+        <v>5023.04798878373</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>317.533333333333</v>
+      </c>
+      <c r="E20" s="0" t="n">
+        <v>0.0668519078549035</v>
+      </c>
+      <c r="F20" s="15"/>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <f aca="false">LN(10)*$B$27*$B$26*B21</f>
+        <v>6735.45071223273</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>330</v>
+      </c>
+      <c r="E21" s="0" t="n">
+        <v>0.0498556600951823</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="0" t="n">
+        <v>0.0459542747486251</v>
+      </c>
+      <c r="F23" s="0" t="n">
+        <v>0.0229771373743126</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E24" s="0" t="n">
+        <v>0.024282547956706</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="0" t="n">
+        <v>298.15</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="0" t="n">
+        <v>8.314462</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="1048571" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048572" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048573" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>